--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\_Project\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4DE0F8B-4C90-4557-970E-B2865BBE5ACB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DEDC6F-8975-4758-8E34-F0C576BA1EC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="1" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -4007,15 +4007,15 @@
       </c>
       <c r="D38" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E38">
         <f>InputData[[#This Row],[クールタイム]]</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F38">
         <f>InputData[[#This Row],[効果数値]]</f>
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="G38" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -5500,13 +5500,13 @@
         <v>正位置</v>
       </c>
       <c r="C38" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H38" t="s">
         <v>35</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53DEDC6F-8975-4758-8E34-F0C576BA1EC8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF48807-A024-4405-9C29-14A50F785D9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BF48807-A024-4405-9C29-14A50F785D9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DC6597-F329-4401-BCA9-D8D1CA20E184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="165">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1110,6 +1110,68 @@
   </si>
   <si>
     <t>Sprites/Arcana</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Summon</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FlipHorizontally</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Charm</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Blackout</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>EquivalentExchange</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Steel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Trap</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Teleport</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AllAtack</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Counter</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FlipCamera</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Correct</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dimension</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>向いた方向にブリンクをするカード</t>
+    <rPh sb="0" eb="1">
+      <t>ム</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ホウコウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1258,7 +1320,7 @@
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
-      <calculatedColumnFormula>InputData[[#This Row],[効果音]]</calculatedColumnFormula>
+      <calculatedColumnFormula>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
@@ -2295,7 +2357,7 @@
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="13.19921875" customWidth="1"/>
     <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.296875" customWidth="1"/>
     <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
@@ -2365,9 +2427,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H2">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H2" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I2" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2411,9 +2473,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H3">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H3" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I3" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2457,9 +2519,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H4">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H4" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I4" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2503,9 +2565,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Monster</v>
       </c>
-      <c r="H5">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H5" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Summon</v>
       </c>
       <c r="I5" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2549,9 +2611,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H6">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H6" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I6" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2595,9 +2657,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H7">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H7" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I7" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2641,9 +2703,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H8">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H8" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I8" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2687,9 +2749,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Dice</v>
       </c>
-      <c r="H9">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H9" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I9" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2733,9 +2795,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H10">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H10" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I10" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2779,9 +2841,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H11">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H11" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I11" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2825,9 +2887,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H12">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H12" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I12" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2871,9 +2933,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H13">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H13" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/FlipHorizontally</v>
       </c>
       <c r="I13" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2917,9 +2979,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H14">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H14" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Charm</v>
       </c>
       <c r="I14" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2963,9 +3025,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H15">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H15" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Blackout</v>
       </c>
       <c r="I15" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3009,9 +3071,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H16">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H16" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I16" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3055,9 +3117,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H17">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H17" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I17" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3101,9 +3163,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H18">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H18" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I18" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3147,9 +3209,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H19">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H19" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/EquivalentExchange</v>
       </c>
       <c r="I19" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3193,9 +3255,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H20">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H20" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Steel</v>
       </c>
       <c r="I20" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3239,9 +3301,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Trap</v>
       </c>
-      <c r="H21">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H21" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Trap</v>
       </c>
       <c r="I21" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3285,9 +3347,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H22">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H22" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Teleport</v>
       </c>
       <c r="I22" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3331,9 +3393,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H23">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H23" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I23" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3377,9 +3439,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H24">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H24" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/AllAtack</v>
       </c>
       <c r="I24" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3423,9 +3485,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H25">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H25" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Counter</v>
       </c>
       <c r="I25" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3469,9 +3531,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H26">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H26" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/FlipCamera</v>
       </c>
       <c r="I26" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3515,9 +3577,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H27">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H27" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I27" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3561,9 +3623,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H28">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H28" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I28" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3607,9 +3669,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H29">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H29" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I29" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3653,9 +3715,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H30">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H30" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I30" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3699,9 +3761,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H31">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H31" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I31" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3745,9 +3807,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H32">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H32" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I32" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3791,9 +3853,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H33">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H33" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I33" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3837,9 +3899,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Turret</v>
       </c>
-      <c r="H34">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H34" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I34" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3883,9 +3945,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H35">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H35" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Correct</v>
       </c>
       <c r="I35" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3929,9 +3991,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H36">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H36" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I36" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3975,9 +4037,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H37">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H37" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I37" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4021,13 +4083,13 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H38">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H38" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I38" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>向いた方向にブリンクをするカード</v>
       </c>
       <c r="J38" s="1" t="str">
         <f>"Arcana"&amp;TEXT(A38, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -4067,9 +4129,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/Clone</v>
       </c>
-      <c r="H39">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H39" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I39" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4113,9 +4175,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H40">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H40" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I40" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4159,9 +4221,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H41">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H41" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I41" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4205,9 +4267,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/HpBullet</v>
       </c>
-      <c r="H42">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H42" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I42" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4251,9 +4313,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/miniBullet</v>
       </c>
-      <c r="H43">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H43" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I43" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4297,9 +4359,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H44">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H44" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/</v>
       </c>
       <c r="I44" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4343,9 +4405,9 @@
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
         <v>Effect/Arcana/</v>
       </c>
-      <c r="H45">
-        <f>InputData[[#This Row],[効果音]]</f>
-        <v>0</v>
+      <c r="H45" t="str">
+        <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
+        <v>Audio/SE/Dimension</v>
       </c>
       <c r="I45" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4361,7 +4423,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="JsrtSVZYWtqsM+vamaxfnwW6KDjeS8ergY52B5KFDixxAV12yOMwOn788B5MD0Sk+4SDCfMYuevizTiAWnTLKw==" saltValue="oS2zEMxPdy3ezhGbJolCfw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4635,7 +4696,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ryhF4kBA1BKUHN6LbZlBRteHtUgn49kD1H5CK0aTR961ZyZ07Rj4y9OBolArIZYra1E+Cy2bdg1LYF+iYoq1yg==" saltValue="PerIWNDmBJOSMcG9n1sgIg==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
@@ -4773,6 +4833,9 @@
       <c r="F5" t="s">
         <v>96</v>
       </c>
+      <c r="G5" t="s">
+        <v>151</v>
+      </c>
       <c r="H5" t="s">
         <v>100</v>
       </c>
@@ -4952,6 +5015,9 @@
       <c r="E13">
         <v>15</v>
       </c>
+      <c r="G13" t="s">
+        <v>152</v>
+      </c>
       <c r="H13" t="s">
         <v>108</v>
       </c>
@@ -4974,6 +5040,9 @@
       <c r="E14">
         <v>5</v>
       </c>
+      <c r="G14" t="s">
+        <v>153</v>
+      </c>
       <c r="H14" t="s">
         <v>109</v>
       </c>
@@ -4996,6 +5065,9 @@
       <c r="E15">
         <v>10</v>
       </c>
+      <c r="G15" t="s">
+        <v>154</v>
+      </c>
       <c r="H15" t="s">
         <v>110</v>
       </c>
@@ -5084,6 +5156,9 @@
       <c r="E19">
         <v>0.05</v>
       </c>
+      <c r="G19" t="s">
+        <v>155</v>
+      </c>
       <c r="H19" t="s">
         <v>114</v>
       </c>
@@ -5106,6 +5181,9 @@
       <c r="E20">
         <v>-1</v>
       </c>
+      <c r="G20" t="s">
+        <v>156</v>
+      </c>
       <c r="H20" t="s">
         <v>115</v>
       </c>
@@ -5131,6 +5209,9 @@
       <c r="F21" t="s">
         <v>137</v>
       </c>
+      <c r="G21" t="s">
+        <v>157</v>
+      </c>
       <c r="H21" t="s">
         <v>116</v>
       </c>
@@ -5153,6 +5234,9 @@
       <c r="E22">
         <v>-1</v>
       </c>
+      <c r="G22" t="s">
+        <v>158</v>
+      </c>
       <c r="H22" t="s">
         <v>117</v>
       </c>
@@ -5197,6 +5281,9 @@
       <c r="E24">
         <v>15</v>
       </c>
+      <c r="G24" t="s">
+        <v>159</v>
+      </c>
       <c r="H24" t="s">
         <v>140</v>
       </c>
@@ -5219,6 +5306,9 @@
       <c r="E25">
         <v>15</v>
       </c>
+      <c r="G25" t="s">
+        <v>160</v>
+      </c>
       <c r="H25" t="s">
         <v>119</v>
       </c>
@@ -5241,6 +5331,9 @@
       <c r="E26">
         <v>5</v>
       </c>
+      <c r="G26" t="s">
+        <v>161</v>
+      </c>
       <c r="H26" t="s">
         <v>120</v>
       </c>
@@ -5442,6 +5535,9 @@
       <c r="E35">
         <v>0.5</v>
       </c>
+      <c r="G35" t="s">
+        <v>162</v>
+      </c>
       <c r="H35" t="s">
         <v>127</v>
       </c>
@@ -5509,7 +5605,7 @@
         <v>5</v>
       </c>
       <c r="H38" t="s">
-        <v>35</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
@@ -5670,6 +5766,9 @@
       </c>
       <c r="E45">
         <v>-1</v>
+      </c>
+      <c r="G45" t="s">
+        <v>163</v>
       </c>
       <c r="H45" t="s">
         <v>134</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05714d3454c468b4/デスクトップ/Create/Git/Arcanumber2026/Assets/StreamingAssets/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DC6597-F329-4401-BCA9-D8D1CA20E184}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C9DC6597-F329-4401-BCA9-D8D1CA20E184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C4F5E3B-1825-4F21-860A-1F3EC1D749DE}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8124" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
   <sheets>
     <sheet name="アルカナ名" sheetId="1" r:id="rId1"/>
@@ -22,6 +22,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1218,11 +1229,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1279,6 +1287,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B115C581-8351-4C19-88DA-A890D1F26A5A}" name="ArcanaMaster" displayName="ArcanaMaster" ref="A1:D45" totalsRowShown="0">
   <autoFilter ref="A1:D45" xr:uid="{9D910B5F-CE33-4841-83B3-3040E6D3B936}"/>
@@ -1286,7 +1298,7 @@
     <tableColumn id="1" xr3:uid="{65175C44-F81B-4B6B-B85A-4B77B2D8D94C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C1D039E5-540F-4BA0-A810-85236C0CDD0E}" name="位置"/>
     <tableColumn id="3" xr3:uid="{6BE0F20E-0384-4641-936C-55C7A196FF36}" name="名前"/>
-    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="9">
       <calculatedColumnFormula>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1301,34 +1313,34 @@
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="6">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
       <calculatedColumnFormula>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="0">
       <calculatedColumnFormula>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1343,7 +1355,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="10">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1358,9 +1370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1398,7 +1410,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1504,7 +1516,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1646,7 +1658,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1655,14 +1667,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED60381-C300-473B-9D6A-8D8B9047D757}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1676,7 +1688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1691,7 +1703,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1706,7 +1718,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1721,7 +1733,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1736,7 +1748,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1751,7 +1763,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1766,7 +1778,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1781,7 +1793,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1796,7 +1808,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>4</v>
       </c>
@@ -1811,7 +1823,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1826,7 +1838,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1841,7 +1853,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1856,7 +1868,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>6</v>
       </c>
@@ -1871,7 +1883,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1886,7 +1898,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1901,7 +1913,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1916,7 +1928,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1931,7 +1943,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1946,7 +1958,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1961,7 +1973,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1976,7 +1988,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1991,7 +2003,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2006,7 +2018,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>11</v>
       </c>
@@ -2021,7 +2033,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>11</v>
       </c>
@@ -2036,7 +2048,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>12</v>
       </c>
@@ -2051,7 +2063,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>12</v>
       </c>
@@ -2066,7 +2078,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2081,7 +2093,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>13</v>
       </c>
@@ -2096,7 +2108,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2111,7 +2123,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>14</v>
       </c>
@@ -2126,7 +2138,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>15</v>
       </c>
@@ -2141,7 +2153,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>15</v>
       </c>
@@ -2156,7 +2168,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>16</v>
       </c>
@@ -2171,7 +2183,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>16</v>
       </c>
@@ -2186,7 +2198,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>17</v>
       </c>
@@ -2201,7 +2213,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2216,7 +2228,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>18</v>
       </c>
@@ -2231,7 +2243,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2246,7 +2258,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>19</v>
       </c>
@@ -2261,7 +2273,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2276,7 +2288,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>20</v>
       </c>
@@ -2291,7 +2303,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2306,7 +2318,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>21</v>
       </c>
@@ -2321,7 +2333,7 @@
         <v>21World</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2350,20 +2362,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
   <dimension ref="A1:K45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.19921875" customWidth="1"/>
-    <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.296875" customWidth="1"/>
-    <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="51.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2398,7 +2410,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2435,16 +2447,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>HPを上げるカード</v>
       </c>
-      <c r="J2" s="1" t="str">
+      <c r="J2" t="str">
         <f>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolFront</v>
       </c>
-      <c r="K2" s="1" t="str">
+      <c r="K2" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2481,16 +2493,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>何も持たなくても勝てることが証明できるカード</v>
       </c>
-      <c r="J3" s="1" t="str">
+      <c r="J3" t="str">
         <f>"Arcana"&amp;TEXT(A3, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana00FoolBack</v>
       </c>
-      <c r="K3" s="1" t="str">
+      <c r="K3" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2527,16 +2539,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>防御無視を付与できるカード</v>
       </c>
-      <c r="J4" s="1" t="str">
+      <c r="J4" t="str">
         <f>"Arcana"&amp;TEXT(A4, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianFront</v>
       </c>
-      <c r="K4" s="1" t="str">
+      <c r="K4" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2573,16 +2585,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>召喚物を出せるカード</v>
       </c>
-      <c r="J5" s="1" t="str">
+      <c r="J5" t="str">
         <f>"Arcana"&amp;TEXT(A5, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana01MagicianBack</v>
       </c>
-      <c r="K5" s="1" t="str">
+      <c r="K5" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2619,16 +2631,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>時間がたつほど強くなるカード</v>
       </c>
-      <c r="J6" s="1" t="str">
+      <c r="J6" t="str">
         <f>"Arcana"&amp;TEXT(A6, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessFront</v>
       </c>
-      <c r="K6" s="1" t="str">
+      <c r="K6" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2665,16 +2677,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>時間がたつほど弱くなるカード</v>
       </c>
-      <c r="J7" s="1" t="str">
+      <c r="J7" t="str">
         <f>"Arcana"&amp;TEXT(A7, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana02HighPriestessBack</v>
       </c>
-      <c r="K7" s="1" t="str">
+      <c r="K7" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2711,16 +2723,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>自然治癒を付与するカード</v>
       </c>
-      <c r="J8" s="1" t="str">
+      <c r="J8" t="str">
         <f>"Arcana"&amp;TEXT(A8, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressFront</v>
       </c>
-      <c r="K8" s="1" t="str">
+      <c r="K8" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2757,16 +2769,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>ランダムでバフやデバフがつくカード</v>
       </c>
-      <c r="J9" s="1" t="str">
+      <c r="J9" t="str">
         <f>"Arcana"&amp;TEXT(A9, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana03EmpressBack</v>
       </c>
-      <c r="K9" s="1" t="str">
+      <c r="K9" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2803,16 +2815,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキル禁止を付与するカード</v>
       </c>
-      <c r="J10" s="1" t="str">
+      <c r="J10" t="str">
         <f>"Arcana"&amp;TEXT(A10, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorFront</v>
       </c>
-      <c r="K10" s="1" t="str">
+      <c r="K10" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2849,16 +2861,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>通常攻撃は振れないがダメージが上がるカード</v>
       </c>
-      <c r="J11" s="1" t="str">
+      <c r="J11" t="str">
         <f>"Arcana"&amp;TEXT(A11, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana04EmperorBack</v>
       </c>
-      <c r="K11" s="1" t="str">
+      <c r="K11" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2895,16 +2907,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキルの当たり判定が大きくなるカード</v>
       </c>
-      <c r="J12" s="1" t="str">
+      <c r="J12" t="str">
         <f>"Arcana"&amp;TEXT(A12, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantFront</v>
       </c>
-      <c r="K12" s="1" t="str">
+      <c r="K12" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2941,16 +2953,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵の行動を逆にするカード</v>
       </c>
-      <c r="J13" s="1" t="str">
+      <c r="J13" t="str">
         <f>"Arcana"&amp;TEXT(A13, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana05HierophantBack</v>
       </c>
-      <c r="K13" s="1" t="str">
+      <c r="K13" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2987,16 +2999,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵がダメージを肩代わりしてくれるカード</v>
       </c>
-      <c r="J14" s="1" t="str">
+      <c r="J14" t="str">
         <f>"Arcana"&amp;TEXT(A14, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversFront</v>
       </c>
-      <c r="K14" s="1" t="str">
+      <c r="K14" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3033,16 +3045,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分以外の視界を暗くするカード</v>
       </c>
-      <c r="J15" s="1" t="str">
+      <c r="J15" t="str">
         <f>"Arcana"&amp;TEXT(A15, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana06LoversBack</v>
       </c>
-      <c r="K15" s="1" t="str">
+      <c r="K15" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3079,16 +3091,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>移動速度が速くなるカード</v>
       </c>
-      <c r="J16" s="1" t="str">
+      <c r="J16" t="str">
         <f>"Arcana"&amp;TEXT(A16, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotFront</v>
       </c>
-      <c r="K16" s="1" t="str">
+      <c r="K16" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3125,16 +3137,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>スキル発動の予備動作の時間が半分になるカード</v>
       </c>
-      <c r="J17" s="1" t="str">
+      <c r="J17" t="str">
         <f>"Arcana"&amp;TEXT(A17, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana07ChariotBack</v>
       </c>
-      <c r="K17" s="1" t="str">
+      <c r="K17" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3171,16 +3183,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>攻撃力を上げるカード</v>
       </c>
-      <c r="J18" s="1" t="str">
+      <c r="J18" t="str">
         <f>"Arcana"&amp;TEXT(A18, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthFront</v>
       </c>
-      <c r="K18" s="1" t="str">
+      <c r="K18" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3217,16 +3229,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>HPが減るたび他のステータスが上がるカード</v>
       </c>
-      <c r="J19" s="1" t="str">
+      <c r="J19" t="str">
         <f>"Arcana"&amp;TEXT(A19, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana08StrengthBack</v>
       </c>
-      <c r="K19" s="1" t="str">
+      <c r="K19" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3263,16 +3275,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>人が回復したHPを半分奪うカード</v>
       </c>
-      <c r="J20" s="1" t="str">
+      <c r="J20" t="str">
         <f>"Arcana"&amp;TEXT(A20, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitFront</v>
       </c>
-      <c r="K20" s="1" t="str">
+      <c r="K20" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3309,16 +3321,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>トラップを設置するカード</v>
       </c>
-      <c r="J21" s="1" t="str">
+      <c r="J21" t="str">
         <f>"Arcana"&amp;TEXT(A21, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana09HermitBack</v>
       </c>
-      <c r="K21" s="1" t="str">
+      <c r="K21" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3355,16 +3367,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>ランダムな場所にテレポートするカード</v>
       </c>
-      <c r="J22" s="1" t="str">
+      <c r="J22" t="str">
         <f>"Arcana"&amp;TEXT(A22, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneFront</v>
       </c>
-      <c r="K22" s="1" t="str">
+      <c r="K22" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3401,16 +3413,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵をジャンプ禁止にするカード</v>
       </c>
-      <c r="J23" s="1" t="str">
+      <c r="J23" t="str">
         <f>"Arcana"&amp;TEXT(A23, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana10WheelOfFortuneBack</v>
       </c>
-      <c r="K23" s="1" t="str">
+      <c r="K23" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3447,16 +3459,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵に一定のダメージを与えるカード</v>
       </c>
-      <c r="J24" s="1" t="str">
+      <c r="J24" t="str">
         <f>"Arcana"&amp;TEXT(A24, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeFront</v>
       </c>
-      <c r="K24" s="1" t="str">
+      <c r="K24" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3493,16 +3505,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>カウンターを付与するカード</v>
       </c>
-      <c r="J25" s="1" t="str">
+      <c r="J25" t="str">
         <f>"Arcana"&amp;TEXT(A25, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana11JusticeBack</v>
       </c>
-      <c r="K25" s="1" t="str">
+      <c r="K25" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3539,16 +3551,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>視点が反対になるカード</v>
       </c>
-      <c r="J26" s="1" t="str">
+      <c r="J26" t="str">
         <f>"Arcana"&amp;TEXT(A26, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManFront</v>
       </c>
-      <c r="K26" s="1" t="str">
+      <c r="K26" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3585,16 +3597,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>運気が上がるカード</v>
       </c>
-      <c r="J27" s="1" t="str">
+      <c r="J27" t="str">
         <f>"Arcana"&amp;TEXT(A27, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana12HangedManBack</v>
       </c>
-      <c r="K27" s="1" t="str">
+      <c r="K27" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3609,7 +3621,7 @@
       </c>
       <c r="D28" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>SkillEffect</v>
       </c>
       <c r="E28">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -3631,16 +3643,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>攻撃を降るたびにダメージを受けるが攻撃力が上がるカード</v>
       </c>
-      <c r="J28" s="1" t="str">
+      <c r="J28" t="str">
         <f>"Arcana"&amp;TEXT(A28, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathFront</v>
       </c>
-      <c r="K28" s="1" t="str">
+      <c r="K28" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3677,16 +3689,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>相手にダメージを与えたときに回復するカード</v>
       </c>
-      <c r="J29" s="1" t="str">
+      <c r="J29" t="str">
         <f>"Arcana"&amp;TEXT(A29, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana13DeathBack</v>
       </c>
-      <c r="K29" s="1" t="str">
+      <c r="K29" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3723,16 +3735,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分のスキルのクールタイムを早くするカード</v>
       </c>
-      <c r="J30" s="1" t="str">
+      <c r="J30" t="str">
         <f>"Arcana"&amp;TEXT(A30, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceFront</v>
       </c>
-      <c r="K30" s="1" t="str">
+      <c r="K30" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3769,16 +3781,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵のクールタイムを遅くするカード</v>
       </c>
-      <c r="J31" s="1" t="str">
+      <c r="J31" t="str">
         <f>"Arcana"&amp;TEXT(A31, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana14TemperanceBack</v>
       </c>
-      <c r="K31" s="1" t="str">
+      <c r="K31" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3815,16 +3827,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>#</v>
       </c>
-      <c r="J32" s="1" t="str">
+      <c r="J32" t="str">
         <f>"Arcana"&amp;TEXT(A32, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilFront</v>
       </c>
-      <c r="K32" s="1" t="str">
+      <c r="K32" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3861,16 +3873,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>自分のバフ・デバフを消し、その分攻撃力が上がるカード</v>
       </c>
-      <c r="J33" s="1" t="str">
+      <c r="J33" t="str">
         <f>"Arcana"&amp;TEXT(A33, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana15DevilBack</v>
       </c>
-      <c r="K33" s="1" t="str">
+      <c r="K33" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3907,16 +3919,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>タレットがおけるカード</v>
       </c>
-      <c r="J34" s="1" t="str">
+      <c r="J34" t="str">
         <f>"Arcana"&amp;TEXT(A34, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerFront</v>
       </c>
-      <c r="K34" s="1" t="str">
+      <c r="K34" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3953,16 +3965,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>確率で数秒後にスキルが再発動するカード</v>
       </c>
-      <c r="J35" s="1" t="str">
+      <c r="J35" t="str">
         <f>"Arcana"&amp;TEXT(A35, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana16TowerBack</v>
       </c>
-      <c r="K35" s="1" t="str">
+      <c r="K35" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -3999,16 +4011,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>あなたが注目を浴びるカード</v>
       </c>
-      <c r="J36" s="1" t="str">
+      <c r="J36" t="str">
         <f>"Arcana"&amp;TEXT(A36, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarFront</v>
       </c>
-      <c r="K36" s="1" t="str">
+      <c r="K36" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4045,16 +4057,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>無敵を付与するカード</v>
       </c>
-      <c r="J37" s="1" t="str">
+      <c r="J37" t="str">
         <f>"Arcana"&amp;TEXT(A37, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana17StarBack</v>
       </c>
-      <c r="K37" s="1" t="str">
+      <c r="K37" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4091,16 +4103,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>向いた方向にブリンクをするカード</v>
       </c>
-      <c r="J38" s="1" t="str">
+      <c r="J38" t="str">
         <f>"Arcana"&amp;TEXT(A38, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonFront</v>
       </c>
-      <c r="K38" s="1" t="str">
+      <c r="K38" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4115,7 +4127,7 @@
       </c>
       <c r="D39" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>Command</v>
       </c>
       <c r="E39">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -4137,16 +4149,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>分身が出てくるカード</v>
       </c>
-      <c r="J39" s="1" t="str">
+      <c r="J39" t="str">
         <f>"Arcana"&amp;TEXT(A39, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana18MoonBack</v>
       </c>
-      <c r="K39" s="1" t="str">
+      <c r="K39" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4183,16 +4195,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>晴れ日和になるカード</v>
       </c>
-      <c r="J40" s="1" t="str">
+      <c r="J40" t="str">
         <f>"Arcana"&amp;TEXT(A40, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunFront</v>
       </c>
-      <c r="K40" s="1" t="str">
+      <c r="K40" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4229,16 +4241,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>敵をスタンするカード</v>
       </c>
-      <c r="J41" s="1" t="str">
+      <c r="J41" t="str">
         <f>"Arcana"&amp;TEXT(A41, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana19SunBack</v>
       </c>
-      <c r="K41" s="1" t="str">
+      <c r="K41" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4275,16 +4287,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>当たると現在HPの30％のHPを減らす弾を打つ</v>
       </c>
-      <c r="J42" s="1" t="str">
+      <c r="J42" t="str">
         <f>"Arcana"&amp;TEXT(A42, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementFront</v>
       </c>
-      <c r="K42" s="1" t="str">
+      <c r="K42" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4321,16 +4333,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>銃弾の雨が降ってくるカード</v>
       </c>
-      <c r="J43" s="1" t="str">
+      <c r="J43" t="str">
         <f>"Arcana"&amp;TEXT(A43, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana20JudgementBack</v>
       </c>
-      <c r="K43" s="1" t="str">
+      <c r="K43" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4367,16 +4379,16 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>二段ジャンプができるカード</v>
       </c>
-      <c r="J44" s="1" t="str">
+      <c r="J44" t="str">
         <f>"Arcana"&amp;TEXT(A44, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldFront</v>
       </c>
-      <c r="K44" s="1" t="str">
+      <c r="K44" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/21World</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4413,11 +4425,11 @@
         <f>InputData[[#This Row],[説明]]</f>
         <v>次元移動ができるカード</v>
       </c>
-      <c r="J45" s="1" t="str">
+      <c r="J45" t="str">
         <f>"Arcana"&amp;TEXT(A45, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
         <v>Arcana21WorldBack</v>
       </c>
-      <c r="K45" s="1" t="str">
+      <c r="K45" t="str">
         <f>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</f>
         <v>Sprites/Arcana/21World</v>
       </c>
@@ -4435,34 +4447,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA57FC-DF38-4EEA-B04B-DBAD106E9B87}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.19921875" customWidth="1"/>
+    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="D1" s="2" t="s">
+      <c r="B1" s="1"/>
+      <c r="D1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="2"/>
+      <c r="E1" s="1"/>
       <c r="G1" t="s">
         <v>82</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -4485,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -4505,7 +4517,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -4522,7 +4534,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -4539,7 +4551,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -4553,7 +4565,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D7" t="s">
         <v>41</v>
       </c>
@@ -4564,7 +4576,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D8" t="s">
         <v>42</v>
       </c>
@@ -4575,7 +4587,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D9" t="s">
         <v>43</v>
       </c>
@@ -4583,7 +4595,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D10" t="s">
         <v>44</v>
       </c>
@@ -4591,7 +4603,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D11" t="s">
         <v>45</v>
       </c>
@@ -4599,7 +4611,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D12" t="s">
         <v>46</v>
       </c>
@@ -4607,7 +4619,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D13" t="s">
         <v>47</v>
       </c>
@@ -4615,7 +4627,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D14" t="s">
         <v>48</v>
       </c>
@@ -4623,7 +4635,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D15" t="s">
         <v>49</v>
       </c>
@@ -4631,7 +4643,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="D16" t="s">
         <v>50</v>
       </c>
@@ -4639,7 +4651,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D17" t="s">
         <v>51</v>
       </c>
@@ -4647,7 +4659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D18" t="s">
         <v>52</v>
       </c>
@@ -4655,7 +4667,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D19" t="s">
         <v>53</v>
       </c>
@@ -4663,7 +4675,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D20" t="s">
         <v>54</v>
       </c>
@@ -4671,7 +4683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D21" t="s">
         <v>55</v>
       </c>
@@ -4679,7 +4691,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D22" t="s">
         <v>56</v>
       </c>
@@ -4687,7 +4699,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.4">
       <c r="D23" t="s">
         <v>57</v>
       </c>
@@ -4710,17 +4722,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C49A0F-8337-4201-B700-EC3BC8157248}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" customWidth="1"/>
-    <col min="7" max="7" width="26.09765625" customWidth="1"/>
-    <col min="8" max="8" width="75.8984375" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="26.125" customWidth="1"/>
+    <col min="8" max="8" width="75.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4746,7 +4758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4768,7 +4780,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4790,7 +4802,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4812,7 +4824,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4840,7 +4852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4862,7 +4874,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4884,7 +4896,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4906,7 +4918,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4931,7 +4943,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4953,7 +4965,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4975,7 +4987,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -4997,7 +5009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5022,7 +5034,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5047,7 +5059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5072,7 +5084,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5094,7 +5106,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5116,7 +5128,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5138,7 +5150,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5163,7 +5175,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5188,7 +5200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5216,7 +5228,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5241,7 +5253,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5263,7 +5275,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5288,7 +5300,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5313,7 +5325,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5338,7 +5350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5360,7 +5372,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5370,7 +5382,7 @@
         <v>正位置</v>
       </c>
       <c r="C28" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -5382,7 +5394,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5404,7 +5416,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5426,7 +5438,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5448,7 +5460,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5470,7 +5482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5492,7 +5504,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5517,7 +5529,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5542,7 +5554,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5564,7 +5576,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5586,7 +5598,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5608,7 +5620,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5618,7 +5630,7 @@
         <v>逆位置</v>
       </c>
       <c r="C39" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D39">
         <v>45</v>
@@ -5633,7 +5645,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5655,7 +5667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5677,7 +5689,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5702,7 +5714,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5727,7 +5739,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -5749,7 +5761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05714d3454c468b4/デスクトップ/Create/Git/Arcanumber2026/Assets/StreamingAssets/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{C9DC6597-F329-4401-BCA9-D8D1CA20E184}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C4F5E3B-1825-4F21-860A-1F3EC1D749DE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01384114-BBC9-4F20-B4D4-10FC7BD83F2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,10 +28,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1298,7 +1298,7 @@
     <tableColumn id="1" xr3:uid="{65175C44-F81B-4B6B-B85A-4B77B2D8D94C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C1D039E5-540F-4BA0-A810-85236C0CDD0E}" name="位置"/>
     <tableColumn id="3" xr3:uid="{6BE0F20E-0384-4641-936C-55C7A196FF36}" name="名前"/>
-    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="10">
       <calculatedColumnFormula>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1313,34 +1313,34 @@
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="9">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="7">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="1">
       <calculatedColumnFormula>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1355,7 +1355,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="0">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1370,9 +1370,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1410,7 +1410,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1516,7 +1516,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1658,7 +1658,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1667,14 +1667,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED60381-C300-473B-9D6A-8D8B9047D757}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1718,7 +1718,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1763,7 +1763,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1793,7 +1793,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1808,7 +1808,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>4</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>6</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1913,7 +1913,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1943,7 +1943,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1973,7 +1973,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1988,7 +1988,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -2003,7 +2003,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>11</v>
       </c>
@@ -2033,7 +2033,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>11</v>
       </c>
@@ -2048,7 +2048,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>12</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>12</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>13</v>
       </c>
@@ -2108,7 +2108,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2123,7 +2123,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>14</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>15</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>15</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>16</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>16</v>
       </c>
@@ -2198,7 +2198,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>17</v>
       </c>
@@ -2213,7 +2213,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>18</v>
       </c>
@@ -2243,7 +2243,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2258,7 +2258,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>19</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2288,7 +2288,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>20</v>
       </c>
@@ -2303,7 +2303,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>21</v>
       </c>
@@ -2333,7 +2333,7 @@
         <v>21World</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2362,20 +2362,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
   <dimension ref="A1:K45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="9" width="51.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.19921875" customWidth="1"/>
+    <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.19921875" customWidth="1"/>
+    <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2410,7 +2410,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2456,7 +2456,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2502,7 +2502,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2548,7 +2548,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2594,7 +2594,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2640,7 +2640,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2686,7 +2686,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2732,7 +2732,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2778,7 +2778,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2824,7 +2824,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2870,7 +2870,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2916,7 +2916,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2962,7 +2962,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3008,7 +3008,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3054,7 +3054,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3100,7 +3100,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3146,7 +3146,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3192,7 +3192,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3238,7 +3238,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3284,7 +3284,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3330,7 +3330,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3376,7 +3376,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3422,7 +3422,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3468,7 +3468,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3514,7 +3514,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3560,7 +3560,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3606,7 +3606,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3652,7 +3652,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3698,7 +3698,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3744,7 +3744,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3790,7 +3790,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3836,7 +3836,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3882,7 +3882,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3928,7 +3928,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3974,7 +3974,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4020,7 +4020,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4066,7 +4066,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4112,7 +4112,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4158,7 +4158,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4204,7 +4204,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4250,7 +4250,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4296,7 +4296,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4342,7 +4342,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4388,7 +4388,7 @@
         <v>Sprites/Arcana/21World</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4447,17 +4447,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA57FC-DF38-4EEA-B04B-DBAD106E9B87}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4474,7 +4474,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -4497,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -4517,7 +4517,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>93</v>
       </c>
@@ -4534,7 +4534,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>94</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>95</v>
       </c>
@@ -4565,7 +4565,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D7" t="s">
         <v>41</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
         <v>42</v>
       </c>
@@ -4587,7 +4587,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
         <v>43</v>
       </c>
@@ -4595,7 +4595,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
         <v>44</v>
       </c>
@@ -4603,7 +4603,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
         <v>45</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>46</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
         <v>47</v>
       </c>
@@ -4627,7 +4627,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
         <v>48</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D15" t="s">
         <v>49</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D16" t="s">
         <v>50</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D17" t="s">
         <v>51</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D18" t="s">
         <v>52</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
         <v>53</v>
       </c>
@@ -4675,7 +4675,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
         <v>54</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
         <v>55</v>
       </c>
@@ -4691,7 +4691,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
         <v>56</v>
       </c>
@@ -4699,7 +4699,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D23" t="s">
         <v>57</v>
       </c>
@@ -4722,17 +4722,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C49A0F-8337-4201-B700-EC3BC8157248}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.25" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="26.125" customWidth="1"/>
-    <col min="8" max="8" width="75.875" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" customWidth="1"/>
+    <col min="7" max="7" width="26.09765625" customWidth="1"/>
+    <col min="8" max="8" width="75.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4780,7 +4780,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4802,7 +4802,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4824,7 +4824,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4852,7 +4852,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4874,7 +4874,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4896,7 +4896,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4918,7 +4918,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4943,7 +4943,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4965,7 +4965,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4987,7 +4987,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5009,7 +5009,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5034,7 +5034,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5059,7 +5059,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5084,7 +5084,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5106,7 +5106,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5128,7 +5128,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5150,7 +5150,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5175,7 +5175,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5200,7 +5200,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5228,7 +5228,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5253,7 +5253,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5275,7 +5275,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5300,7 +5300,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5325,7 +5325,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5350,7 +5350,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5372,7 +5372,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5394,7 +5394,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5416,7 +5416,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5438,7 +5438,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5460,7 +5460,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5482,7 +5482,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5504,7 +5504,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5529,7 +5529,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5554,7 +5554,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5576,7 +5576,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5598,7 +5598,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5620,7 +5620,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5645,7 +5645,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5667,7 +5667,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5689,7 +5689,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5714,7 +5714,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5739,7 +5739,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -5761,7 +5761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01384114-BBC9-4F20-B4D4-10FC7BD83F2A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -22,17 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4319,7 +4308,7 @@
       </c>
       <c r="F43">
         <f>InputData[[#This Row],[効果数値]]</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G43" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
@@ -5730,7 +5719,7 @@
         <v>45</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F43" t="s">
         <v>139</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05714d3454c468b4/デスクトップ/Create/Git/Arcanumber2026/Assets/StreamingAssets/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844DCA30-4A3B-413B-B6B3-6EE043824331}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="167">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -266,10 +277,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>#</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>愚者</t>
     <rPh sb="0" eb="2">
       <t>グシャ</t>
@@ -1173,6 +1180,22 @@
       <t>ホウコウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LoversAura</t>
+  </si>
+  <si>
+    <t>防御力を上げるカード</t>
+    <rPh sb="0" eb="3">
+      <t>ボウギョリョク</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Barria</t>
   </si>
 </sst>
 </file>
@@ -1276,10 +1299,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B115C581-8351-4C19-88DA-A890D1F26A5A}" name="ArcanaMaster" displayName="ArcanaMaster" ref="A1:D45" totalsRowShown="0">
   <autoFilter ref="A1:D45" xr:uid="{9D910B5F-CE33-4841-83B3-3040E6D3B936}"/>
@@ -1287,7 +1306,7 @@
     <tableColumn id="1" xr3:uid="{65175C44-F81B-4B6B-B85A-4B77B2D8D94C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C1D039E5-540F-4BA0-A810-85236C0CDD0E}" name="位置"/>
     <tableColumn id="3" xr3:uid="{6BE0F20E-0384-4641-936C-55C7A196FF36}" name="名前"/>
-    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="10">
+    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="9">
       <calculatedColumnFormula>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1302,34 +1321,34 @@
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="9">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="8">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="7">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="6">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
       <calculatedColumnFormula>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="1">
+    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="0">
       <calculatedColumnFormula>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1344,7 +1363,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="10">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1359,9 +1378,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1399,7 +1418,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1505,7 +1524,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1647,7 +1666,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1656,14 +1675,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED60381-C300-473B-9D6A-8D8B9047D757}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.8984375" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1677,7 +1696,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1692,7 +1711,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1707,7 +1726,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1722,7 +1741,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1737,7 +1756,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1752,7 +1771,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1767,7 +1786,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1782,7 +1801,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1797,7 +1816,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>4</v>
       </c>
@@ -1812,7 +1831,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1827,7 +1846,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1842,7 +1861,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1857,7 +1876,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>6</v>
       </c>
@@ -1872,7 +1891,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1887,7 +1906,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1902,7 +1921,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1917,7 +1936,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1932,7 +1951,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1947,7 +1966,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1962,7 +1981,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>9</v>
       </c>
@@ -1977,7 +1996,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>10</v>
       </c>
@@ -1992,7 +2011,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2007,7 +2026,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>11</v>
       </c>
@@ -2022,7 +2041,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>11</v>
       </c>
@@ -2037,7 +2056,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>12</v>
       </c>
@@ -2052,7 +2071,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>12</v>
       </c>
@@ -2067,7 +2086,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2082,7 +2101,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>13</v>
       </c>
@@ -2097,7 +2116,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2112,7 +2131,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>14</v>
       </c>
@@ -2127,7 +2146,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>15</v>
       </c>
@@ -2142,7 +2161,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>15</v>
       </c>
@@ -2157,7 +2176,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>16</v>
       </c>
@@ -2172,7 +2191,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>16</v>
       </c>
@@ -2187,7 +2206,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>17</v>
       </c>
@@ -2202,7 +2221,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2217,7 +2236,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>18</v>
       </c>
@@ -2232,7 +2251,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2247,7 +2266,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>19</v>
       </c>
@@ -2262,7 +2281,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2277,7 +2296,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>20</v>
       </c>
@@ -2292,7 +2311,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2307,7 +2326,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>21</v>
       </c>
@@ -2322,7 +2341,7 @@
         <v>21World</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2351,20 +2370,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
   <dimension ref="A1:K45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.19921875" customWidth="1"/>
-    <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.19921875" customWidth="1"/>
-    <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="20.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" customWidth="1"/>
+    <col min="9" max="9" width="51.375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2381,7 +2400,7 @@
         <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="G1" t="s">
         <v>6</v>
@@ -2393,13 +2412,13 @@
         <v>3</v>
       </c>
       <c r="J1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="K1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2445,7 +2464,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2491,7 +2510,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2537,7 +2556,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2583,7 +2602,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2629,7 +2648,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2675,7 +2694,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2721,7 +2740,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2767,7 +2786,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2813,7 +2832,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2859,7 +2878,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2905,7 +2924,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2951,7 +2970,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -2978,7 +2997,7 @@
       </c>
       <c r="G14" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/LoversAura</v>
       </c>
       <c r="H14" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -2997,7 +3016,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3043,7 +3062,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3089,7 +3108,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3135,7 +3154,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3181,7 +3200,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3227,7 +3246,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3273,7 +3292,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3319,7 +3338,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3365,7 +3384,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3411,7 +3430,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3457,7 +3476,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3484,7 +3503,7 @@
       </c>
       <c r="G25" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Barria</v>
       </c>
       <c r="H25" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -3503,7 +3522,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3549,7 +3568,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3595,7 +3614,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3641,7 +3660,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3687,7 +3706,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3733,7 +3752,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3779,7 +3798,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3814,7 +3833,7 @@
       </c>
       <c r="I32" t="str">
         <f>InputData[[#This Row],[説明]]</f>
-        <v>#</v>
+        <v>防御力を上げるカード</v>
       </c>
       <c r="J32" t="str">
         <f>"Arcana"&amp;TEXT(A32, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</f>
@@ -3825,7 +3844,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3871,7 +3890,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3917,7 +3936,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3963,7 +3982,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4009,7 +4028,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4055,7 +4074,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4101,7 +4120,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4147,7 +4166,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4193,7 +4212,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4239,7 +4258,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4285,7 +4304,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4331,7 +4350,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4377,7 +4396,7 @@
         <v>Sprites/Arcana/21World</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4436,264 +4455,264 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA57FC-DF38-4EEA-B04B-DBAD106E9B87}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="18.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.69921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.19921875" customWidth="1"/>
+    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1"/>
       <c r="G1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="J2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>33</v>
       </c>
       <c r="B3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J3">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" t="s">
         <v>89</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D4" t="s">
         <v>37</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>60</v>
       </c>
-      <c r="I3" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+      <c r="G4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" t="s">
         <v>93</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>90</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" t="s">
         <v>38</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E5" t="s">
         <v>61</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" t="s">
         <v>94</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>91</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" t="s">
         <v>62</v>
       </c>
-      <c r="G5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D6" t="s">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D7" t="s">
         <v>40</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D7" t="s">
+      <c r="G7" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D8" t="s">
         <v>41</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="G7" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D8" t="s">
+      <c r="G8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D9" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>65</v>
       </c>
-      <c r="G8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D9" t="s">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D10" t="s">
         <v>43</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D10" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D11" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D11" t="s">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D12" t="s">
         <v>45</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D12" t="s">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D13" t="s">
         <v>46</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D13" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D14" t="s">
         <v>47</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E14" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D14" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D15" t="s">
         <v>48</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E15" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D15" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E16" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="D16" t="s">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D17" t="s">
         <v>50</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E17" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D17" t="s">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D18" t="s">
         <v>51</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D18" t="s">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D19" t="s">
         <v>52</v>
       </c>
-      <c r="E18" t="s">
+      <c r="E19" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D19" t="s">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D20" t="s">
         <v>53</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E20" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D20" t="s">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D21" t="s">
         <v>54</v>
       </c>
-      <c r="E20" t="s">
+      <c r="E21" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D21" t="s">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D22" t="s">
         <v>55</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D22" t="s">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.4">
+      <c r="D23" t="s">
         <v>56</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.45">
-      <c r="D23" t="s">
-        <v>57</v>
-      </c>
-      <c r="E23" t="s">
-        <v>80</v>
       </c>
     </row>
   </sheetData>
@@ -4711,17 +4730,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C49A0F-8337-4201-B700-EC3BC8157248}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.19921875" customWidth="1"/>
-    <col min="6" max="6" width="19.19921875" customWidth="1"/>
-    <col min="7" max="7" width="26.09765625" customWidth="1"/>
-    <col min="8" max="8" width="75.8984375" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="26.125" customWidth="1"/>
+    <col min="8" max="8" width="75.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4735,7 +4754,7 @@
         <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F1" t="s">
         <v>6</v>
@@ -4747,7 +4766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A2" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4766,10 +4785,10 @@
         <v>1.3</v>
       </c>
       <c r="H2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A3" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4788,10 +4807,10 @@
         <v>-1</v>
       </c>
       <c r="H3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A4" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4810,10 +4829,10 @@
         <v>-1</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A5" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4832,16 +4851,16 @@
         <v>3</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A6" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4860,10 +4879,10 @@
         <v>1.05</v>
       </c>
       <c r="H6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A7" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4882,10 +4901,10 @@
         <v>0.99</v>
       </c>
       <c r="H7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A8" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4904,10 +4923,10 @@
         <v>1</v>
       </c>
       <c r="H8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A9" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4926,13 +4945,13 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A10" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4951,10 +4970,10 @@
         <v>15</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A11" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4973,10 +4992,10 @@
         <v>-1</v>
       </c>
       <c r="H11" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A12" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -4995,10 +5014,10 @@
         <v>0.3</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A13" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5017,13 +5036,13 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H13" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A14" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5041,14 +5060,17 @@
       <c r="E14">
         <v>5</v>
       </c>
+      <c r="F14" t="s">
+        <v>164</v>
+      </c>
       <c r="G14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H14" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A15" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5067,13 +5089,13 @@
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A16" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5092,10 +5114,10 @@
         <v>1.5</v>
       </c>
       <c r="H16" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A17" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5114,10 +5136,10 @@
         <v>1</v>
       </c>
       <c r="H17" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A18" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5136,10 +5158,10 @@
         <v>1.2</v>
       </c>
       <c r="H18" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A19" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5149,7 +5171,7 @@
         <v>逆位置</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19">
         <v>-1</v>
@@ -5158,13 +5180,13 @@
         <v>0.05</v>
       </c>
       <c r="G19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A20" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5183,13 +5205,13 @@
         <v>-1</v>
       </c>
       <c r="G20" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A21" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5208,16 +5230,16 @@
         <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G21" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H21" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A22" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5236,13 +5258,13 @@
         <v>-1</v>
       </c>
       <c r="G22" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H22" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A23" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5261,10 +5283,10 @@
         <v>10</v>
       </c>
       <c r="H23" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A24" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5283,13 +5305,13 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H24" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A25" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5307,14 +5329,17 @@
       <c r="E25">
         <v>15</v>
       </c>
+      <c r="F25" t="s">
+        <v>166</v>
+      </c>
       <c r="G25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H25" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A26" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5333,13 +5358,13 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H26" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A27" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5358,10 +5383,10 @@
         <v>-1</v>
       </c>
       <c r="H27" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A28" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5371,7 +5396,7 @@
         <v>正位置</v>
       </c>
       <c r="C28" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D28">
         <v>-1</v>
@@ -5380,10 +5405,10 @@
         <v>1</v>
       </c>
       <c r="H28" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A29" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5393,7 +5418,7 @@
         <v>逆位置</v>
       </c>
       <c r="C29" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D29">
         <v>-1</v>
@@ -5402,10 +5427,10 @@
         <v>-1</v>
       </c>
       <c r="H29" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A30" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5424,10 +5449,10 @@
         <v>0.2</v>
       </c>
       <c r="H30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A31" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5446,10 +5471,10 @@
         <v>0.2</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A32" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5468,10 +5493,10 @@
         <v>-1</v>
       </c>
       <c r="H32" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A33" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5490,10 +5515,10 @@
         <v>0.05</v>
       </c>
       <c r="H33" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A34" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5512,13 +5537,13 @@
         <v>-1</v>
       </c>
       <c r="F34" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H34" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A35" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5537,13 +5562,13 @@
         <v>0.5</v>
       </c>
       <c r="G35" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H35" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A36" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5562,10 +5587,10 @@
         <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A37" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5584,10 +5609,10 @@
         <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A38" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5606,10 +5631,10 @@
         <v>5</v>
       </c>
       <c r="H38" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A39" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5628,13 +5653,13 @@
         <v>3</v>
       </c>
       <c r="F39" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H39" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A40" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5653,10 +5678,10 @@
         <v>15</v>
       </c>
       <c r="H40" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A41" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5675,10 +5700,10 @@
         <v>3</v>
       </c>
       <c r="H41" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A42" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5697,13 +5722,13 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
+        <v>143</v>
+      </c>
+      <c r="H42" t="s">
         <v>144</v>
       </c>
-      <c r="H42" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A43" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5722,13 +5747,13 @@
         <v>4</v>
       </c>
       <c r="F43" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H43" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A44" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -5747,10 +5772,10 @@
         <v>-1</v>
       </c>
       <c r="H44" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A45" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -5769,10 +5794,10 @@
         <v>-1</v>
       </c>
       <c r="G45" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05714d3454c468b4/デスクトップ/Create/Git/Arcanumber2026/Assets/StreamingAssets/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{844DCA30-4A3B-413B-B6B3-6EE043824331}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72662267-2752-44CE-8BD9-334BDD41D4F0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="168">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1196,6 +1196,9 @@
   </si>
   <si>
     <t>Barria</t>
+  </si>
+  <si>
+    <t>konran</t>
   </si>
 </sst>
 </file>
@@ -1297,6 +1300,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2951,7 +2958,7 @@
       </c>
       <c r="G13" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/konran</v>
       </c>
       <c r="H13" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -5034,6 +5041,9 @@
       </c>
       <c r="E13">
         <v>15</v>
+      </c>
+      <c r="F13" t="s">
+        <v>167</v>
       </c>
       <c r="G13" t="s">
         <v>151</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/05714d3454c468b4/デスクトップ/Create/Git/Arcanumber2026/Assets/StreamingAssets/Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{7636A196-9586-41A3-A6B8-F6CA7197415F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72662267-2752-44CE-8BD9-334BDD41D4F0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35881859-EA36-40BA-A30C-80A5B0C36A56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -23,23 +23,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="172">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1199,6 +1188,20 @@
   </si>
   <si>
     <t>konran</t>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Debuff</t>
+  </si>
+  <si>
+    <t>Healing</t>
+  </si>
+  <si>
+    <t>Sun</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -1313,7 +1316,7 @@
     <tableColumn id="1" xr3:uid="{65175C44-F81B-4B6B-B85A-4B77B2D8D94C}" name="ID"/>
     <tableColumn id="2" xr3:uid="{C1D039E5-540F-4BA0-A810-85236C0CDD0E}" name="位置"/>
     <tableColumn id="3" xr3:uid="{6BE0F20E-0384-4641-936C-55C7A196FF36}" name="名前"/>
-    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="9">
+    <tableColumn id="4" xr3:uid="{1BB2AF53-AE2E-4EE3-BC16-A160656FF0E8}" name="画像" dataDxfId="10">
       <calculatedColumnFormula>TEXT(A2, "00")&amp;VLOOKUP(ArcanaMaster[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1328,34 +1331,34 @@
     <tableColumn id="1" xr3:uid="{A65AA5B3-5D9F-4A53-8148-4A18A64938A2}" name="ID" totalsRowLabel="集計">
       <calculatedColumnFormula>INDEX(ArcanaMaster[ID], ROW()-1)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="8">
+    <tableColumn id="2" xr3:uid="{8B3AF7D8-90E1-41EA-A326-FEF9F023D495}" name="位置" dataDxfId="9">
       <calculatedColumnFormula>VLOOKUP(ArcanaMaster[[#This Row],[位置]],選択用フィールド!$I$2:$J$3,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{4A1C811B-6B1C-4D9F-BF47-2AB531A152AE}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="7">
+    <tableColumn id="4" xr3:uid="{0BD2B815-7AB6-4889-AB14-173E2739EDD5}" name="発動条件" dataDxfId="8">
       <calculatedColumnFormula>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="6">
+    <tableColumn id="5" xr3:uid="{32000BF7-9753-45FD-B2D6-344E111A7D1C}" name="クールタイム" dataDxfId="7">
       <calculatedColumnFormula>InputData[[#This Row],[クールタイム]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="5">
+    <tableColumn id="10" xr3:uid="{62D4CF48-CF16-4BA3-A2CA-142A0A4DAAA4}" name="効果時間" dataDxfId="6">
       <calculatedColumnFormula>InputData[[#This Row],[効果数値]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="4">
+    <tableColumn id="6" xr3:uid="{55BA9E8F-6644-465A-AB88-421F37320DF0}" name="エフェクト" dataDxfId="5">
       <calculatedColumnFormula>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="3">
+    <tableColumn id="7" xr3:uid="{6B3E9D4E-9BFE-45EB-B383-B8876BCA5578}" name="効果音" dataDxfId="4">
       <calculatedColumnFormula>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="2">
+    <tableColumn id="8" xr3:uid="{DCFB5C57-5B5E-4F36-8AA3-07C99FB1DC34}" name="説明" totalsRowFunction="count" dataDxfId="3">
       <calculatedColumnFormula>InputData[[#This Row],[説明]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="1">
+    <tableColumn id="9" xr3:uid="{8A63BDCB-9472-4EC5-B67D-57234FDEFD85}" name="Key" dataDxfId="2">
       <calculatedColumnFormula>"Arcana"&amp;TEXT(A2, "00")&amp;VLOOKUP(ArcanaData[[#This Row],[名前]],選択用フィールド!$D$2:$E$23,2,FALSE)&amp;ArcanaMaster[[#This Row],[位置]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="0">
+    <tableColumn id="11" xr3:uid="{F0FC27E1-0D0A-4555-A1DD-B8896D370E83}" name="画像" dataDxfId="1">
       <calculatedColumnFormula>選択用フィールド!$G$8&amp;"/"&amp;ArcanaMaster[[#This Row],[画像]]</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1370,7 +1373,7 @@
     <tableColumn id="1" xr3:uid="{943AAEBB-23E9-478C-8557-7FBD3B23051C}" name="名前">
       <calculatedColumnFormula>ArcanaMaster[[#This Row],[名前]]</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="10">
+    <tableColumn id="2" xr3:uid="{8863BAAE-8966-45DE-B9A8-7E5C558E2343}" name="位置" dataDxfId="0">
       <calculatedColumnFormula>IF(ArcanaMaster[[#This Row],[位置]]="Front", "正位置", "逆位置")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{9CC9AC39-DB18-4755-8804-BCD12C30BA72}" name="発動条件"/>
@@ -1385,9 +1388,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1425,7 +1428,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1531,7 +1534,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1673,7 +1676,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1682,14 +1685,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED60381-C300-473B-9D6A-8D8B9047D757}">
   <dimension ref="A1:D45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.875" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.8984375" customWidth="1"/>
     <col min="5" max="5" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1703,7 +1706,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1718,7 +1721,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>0</v>
       </c>
@@ -1733,7 +1736,7 @@
         <v>00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>1</v>
       </c>
@@ -1763,7 +1766,7 @@
         <v>01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>2</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>2</v>
       </c>
@@ -1793,7 +1796,7 @@
         <v>02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>3</v>
       </c>
@@ -1808,7 +1811,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>3</v>
       </c>
@@ -1823,7 +1826,7 @@
         <v>03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>4</v>
       </c>
@@ -1838,7 +1841,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>4</v>
       </c>
@@ -1853,7 +1856,7 @@
         <v>04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12">
         <v>5</v>
       </c>
@@ -1868,7 +1871,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13">
         <v>5</v>
       </c>
@@ -1883,7 +1886,7 @@
         <v>05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14">
         <v>6</v>
       </c>
@@ -1898,7 +1901,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15">
         <v>6</v>
       </c>
@@ -1913,7 +1916,7 @@
         <v>06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16">
         <v>7</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17">
         <v>7</v>
       </c>
@@ -1943,7 +1946,7 @@
         <v>07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18">
         <v>8</v>
       </c>
@@ -1958,7 +1961,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19">
         <v>8</v>
       </c>
@@ -1973,7 +1976,7 @@
         <v>08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20">
         <v>9</v>
       </c>
@@ -1988,7 +1991,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21">
         <v>9</v>
       </c>
@@ -2003,7 +2006,7 @@
         <v>09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22">
         <v>10</v>
       </c>
@@ -2018,7 +2021,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23">
         <v>10</v>
       </c>
@@ -2033,7 +2036,7 @@
         <v>10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24">
         <v>11</v>
       </c>
@@ -2048,7 +2051,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25">
         <v>11</v>
       </c>
@@ -2063,7 +2066,7 @@
         <v>11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26">
         <v>12</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27">
         <v>12</v>
       </c>
@@ -2093,7 +2096,7 @@
         <v>12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28">
         <v>13</v>
       </c>
@@ -2108,7 +2111,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29">
         <v>13</v>
       </c>
@@ -2123,7 +2126,7 @@
         <v>13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30">
         <v>14</v>
       </c>
@@ -2138,7 +2141,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31">
         <v>14</v>
       </c>
@@ -2153,7 +2156,7 @@
         <v>14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32">
         <v>15</v>
       </c>
@@ -2168,7 +2171,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33">
         <v>15</v>
       </c>
@@ -2183,7 +2186,7 @@
         <v>15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34">
         <v>16</v>
       </c>
@@ -2198,7 +2201,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35">
         <v>16</v>
       </c>
@@ -2213,7 +2216,7 @@
         <v>16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A36">
         <v>17</v>
       </c>
@@ -2228,7 +2231,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A37">
         <v>17</v>
       </c>
@@ -2243,7 +2246,7 @@
         <v>17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A38">
         <v>18</v>
       </c>
@@ -2258,7 +2261,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A39">
         <v>18</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A40">
         <v>19</v>
       </c>
@@ -2288,7 +2291,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A41">
         <v>19</v>
       </c>
@@ -2303,7 +2306,7 @@
         <v>19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A42">
         <v>20</v>
       </c>
@@ -2318,7 +2321,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A43">
         <v>20</v>
       </c>
@@ -2333,7 +2336,7 @@
         <v>20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A44">
         <v>21</v>
       </c>
@@ -2348,7 +2351,7 @@
         <v>21World</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A45">
         <v>21</v>
       </c>
@@ -2377,20 +2380,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4CB5D73-7EAF-422C-8FF3-EA2211BD96FE}">
   <dimension ref="A1:K45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="20.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.25" customWidth="1"/>
-    <col min="9" max="9" width="51.375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="28.625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="32.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="13.19921875" customWidth="1"/>
+    <col min="7" max="7" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.19921875" customWidth="1"/>
+    <col min="9" max="9" width="51.3984375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="28.59765625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="32.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2425,7 +2428,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2471,7 +2474,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>0</v>
@@ -2517,7 +2520,7 @@
         <v>Sprites/Arcana/00Fool</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2563,7 +2566,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>1</v>
@@ -2609,7 +2612,7 @@
         <v>Sprites/Arcana/01Magician</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2636,7 +2639,7 @@
       </c>
       <c r="G6" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Buff</v>
       </c>
       <c r="H6" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -2655,7 +2658,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>2</v>
@@ -2682,7 +2685,7 @@
       </c>
       <c r="G7" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Debuff</v>
       </c>
       <c r="H7" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -2701,7 +2704,7 @@
         <v>Sprites/Arcana/02HighPriestess</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A8">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2728,7 +2731,7 @@
       </c>
       <c r="G8" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Healing</v>
       </c>
       <c r="H8" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -2747,7 +2750,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A9">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>3</v>
@@ -2793,7 +2796,7 @@
         <v>Sprites/Arcana/03Empress</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A10">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2839,7 +2842,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A11">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>4</v>
@@ -2885,7 +2888,7 @@
         <v>Sprites/Arcana/04Emperor</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A12">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2931,7 +2934,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A13">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>5</v>
@@ -2977,7 +2980,7 @@
         <v>Sprites/Arcana/05Hierophant</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A14">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3023,7 +3026,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A15">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>6</v>
@@ -3069,7 +3072,7 @@
         <v>Sprites/Arcana/06Lovers</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A16">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3115,7 +3118,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A17">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>7</v>
@@ -3161,7 +3164,7 @@
         <v>Sprites/Arcana/07Chariot</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A18">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3207,7 +3210,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A19">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>8</v>
@@ -3253,7 +3256,7 @@
         <v>Sprites/Arcana/08Strength</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A20">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3299,7 +3302,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A21">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>9</v>
@@ -3345,7 +3348,7 @@
         <v>Sprites/Arcana/09Hermit</v>
       </c>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A22">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3391,7 +3394,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A23">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>10</v>
@@ -3437,7 +3440,7 @@
         <v>Sprites/Arcana/10WheelOfFortune</v>
       </c>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A24">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3483,7 +3486,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A25">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>11</v>
@@ -3529,7 +3532,7 @@
         <v>Sprites/Arcana/11Justice</v>
       </c>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A26">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3575,7 +3578,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A27">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>12</v>
@@ -3621,7 +3624,7 @@
         <v>Sprites/Arcana/12HangedMan</v>
       </c>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A28">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3667,7 +3670,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A29">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>13</v>
@@ -3713,7 +3716,7 @@
         <v>Sprites/Arcana/13Death</v>
       </c>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A30">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3759,7 +3762,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A31">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>14</v>
@@ -3805,7 +3808,7 @@
         <v>Sprites/Arcana/14Temperance</v>
       </c>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A32">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3851,7 +3854,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A33">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>15</v>
@@ -3897,7 +3900,7 @@
         <v>Sprites/Arcana/15Devil</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A34">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3943,7 +3946,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A35">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>16</v>
@@ -3989,7 +3992,7 @@
         <v>Sprites/Arcana/16Tower</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A36">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4035,7 +4038,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A37">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>17</v>
@@ -4081,7 +4084,7 @@
         <v>Sprites/Arcana/17Star</v>
       </c>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A38">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4127,7 +4130,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A39">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>18</v>
@@ -4173,7 +4176,7 @@
         <v>Sprites/Arcana/18Moon</v>
       </c>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A40">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4200,7 +4203,7 @@
       </c>
       <c r="G40" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Sun</v>
       </c>
       <c r="H40" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -4219,7 +4222,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A41">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>19</v>
@@ -4265,7 +4268,7 @@
         <v>Sprites/Arcana/19Sun</v>
       </c>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A42">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4311,7 +4314,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A43">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>20</v>
@@ -4357,7 +4360,7 @@
         <v>Sprites/Arcana/20Judgement</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A44">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4403,7 +4406,7 @@
         <v>Sprites/Arcana/21World</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A45">
         <f>INDEX(ArcanaMaster[ID], ROW()-1)</f>
         <v>21</v>
@@ -4462,17 +4465,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCA57FC-DF38-4EEA-B04B-DBAD106E9B87}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.19921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -4489,7 +4492,7 @@
       </c>
       <c r="J1" s="1"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -4512,7 +4515,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>33</v>
       </c>
@@ -4532,7 +4535,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -4549,7 +4552,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>93</v>
       </c>
@@ -4566,7 +4569,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>94</v>
       </c>
@@ -4580,7 +4583,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D7" t="s">
         <v>40</v>
       </c>
@@ -4591,7 +4594,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D8" t="s">
         <v>41</v>
       </c>
@@ -4602,7 +4605,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D9" t="s">
         <v>42</v>
       </c>
@@ -4610,7 +4613,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D10" t="s">
         <v>43</v>
       </c>
@@ -4618,7 +4621,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D11" t="s">
         <v>44</v>
       </c>
@@ -4626,7 +4629,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D12" t="s">
         <v>45</v>
       </c>
@@ -4634,7 +4637,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D13" t="s">
         <v>46</v>
       </c>
@@ -4642,7 +4645,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D14" t="s">
         <v>47</v>
       </c>
@@ -4650,7 +4653,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D15" t="s">
         <v>48</v>
       </c>
@@ -4658,7 +4661,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
       <c r="D16" t="s">
         <v>49</v>
       </c>
@@ -4666,7 +4669,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="17" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D17" t="s">
         <v>50</v>
       </c>
@@ -4674,7 +4677,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="18" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D18" t="s">
         <v>51</v>
       </c>
@@ -4682,7 +4685,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="19" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="19" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D19" t="s">
         <v>52</v>
       </c>
@@ -4690,7 +4693,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="20" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="20" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D20" t="s">
         <v>53</v>
       </c>
@@ -4698,7 +4701,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="21" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D21" t="s">
         <v>54</v>
       </c>
@@ -4706,7 +4709,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="22" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="22" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D22" t="s">
         <v>55</v>
       </c>
@@ -4714,7 +4717,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="23" spans="4:5" x14ac:dyDescent="0.4">
+    <row r="23" spans="4:5" x14ac:dyDescent="0.45">
       <c r="D23" t="s">
         <v>56</v>
       </c>
@@ -4737,17 +4740,17 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45C49A0F-8337-4201-B700-EC3BC8157248}">
   <dimension ref="A1:H45"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="13.25" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
-    <col min="7" max="7" width="26.125" customWidth="1"/>
-    <col min="8" max="8" width="75.875" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.19921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.19921875" customWidth="1"/>
+    <col min="6" max="6" width="19.19921875" customWidth="1"/>
+    <col min="7" max="7" width="26.09765625" customWidth="1"/>
+    <col min="8" max="8" width="75.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4773,7 +4776,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4795,7 +4798,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>愚者</v>
@@ -4817,7 +4820,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4839,7 +4842,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>魔術師</v>
@@ -4867,7 +4870,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4885,11 +4888,14 @@
       <c r="E6">
         <v>1.05</v>
       </c>
+      <c r="F6" t="s">
+        <v>168</v>
+      </c>
       <c r="H6" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女教皇</v>
@@ -4907,11 +4913,14 @@
       <c r="E7">
         <v>0.99</v>
       </c>
+      <c r="F7" t="s">
+        <v>169</v>
+      </c>
       <c r="H7" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4929,11 +4938,14 @@
       <c r="E8">
         <v>1</v>
       </c>
+      <c r="F8" t="s">
+        <v>170</v>
+      </c>
       <c r="H8" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>女帝</v>
@@ -4958,7 +4970,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -4980,7 +4992,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>皇帝</v>
@@ -5002,7 +5014,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5024,7 +5036,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>教皇</v>
@@ -5052,7 +5064,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5080,7 +5092,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>恋人</v>
@@ -5105,7 +5117,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5127,7 +5139,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>戦車</v>
@@ -5149,7 +5161,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5171,7 +5183,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>力</v>
@@ -5196,7 +5208,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5221,7 +5233,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>隠者</v>
@@ -5249,7 +5261,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5274,7 +5286,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>運命の輪</v>
@@ -5296,7 +5308,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5321,7 +5333,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>正義</v>
@@ -5349,7 +5361,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5374,7 +5386,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>つるされた男</v>
@@ -5396,7 +5408,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5418,7 +5430,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>死神</v>
@@ -5440,7 +5452,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5462,7 +5474,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>節制</v>
@@ -5484,7 +5496,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5506,7 +5518,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>悪魔</v>
@@ -5528,7 +5540,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5553,7 +5565,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>塔</v>
@@ -5578,7 +5590,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5600,7 +5612,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>星</v>
@@ -5622,7 +5634,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5644,7 +5656,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A39" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>月</v>
@@ -5669,7 +5681,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5687,11 +5699,14 @@
       <c r="E40">
         <v>15</v>
       </c>
+      <c r="F40" t="s">
+        <v>171</v>
+      </c>
       <c r="H40" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>太陽</v>
@@ -5713,7 +5728,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5738,7 +5753,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>審判</v>
@@ -5763,7 +5778,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>
@@ -5785,7 +5800,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" t="str">
         <f>ArcanaMaster[[#This Row],[名前]]</f>
         <v>世界</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35881859-EA36-40BA-A30C-80A5B0C36A56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D094CE-D9FA-4F3D-8415-12253E306B6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="176">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1202,6 +1202,20 @@
   <si>
     <t>Sun</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>AtkHeal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>HealSteel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Lightningaura</t>
+  </si>
+  <si>
+    <t>Staraura</t>
   </si>
 </sst>
 </file>
@@ -3237,7 +3251,7 @@
       </c>
       <c r="G19" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Buff</v>
       </c>
       <c r="H19" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -3283,7 +3297,7 @@
       </c>
       <c r="G20" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/HealSteel</v>
       </c>
       <c r="H20" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -3651,7 +3665,7 @@
       </c>
       <c r="G28" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Staraura</v>
       </c>
       <c r="H28" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -3697,7 +3711,7 @@
       </c>
       <c r="G29" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/AtkHeal</v>
       </c>
       <c r="H29" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -4065,7 +4079,7 @@
       </c>
       <c r="G37" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Lightningaura</v>
       </c>
       <c r="H37" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -5201,6 +5215,9 @@
       <c r="E19">
         <v>0.05</v>
       </c>
+      <c r="F19" t="s">
+        <v>168</v>
+      </c>
       <c r="G19" t="s">
         <v>154</v>
       </c>
@@ -5226,6 +5243,9 @@
       <c r="E20">
         <v>-1</v>
       </c>
+      <c r="F20" t="s">
+        <v>173</v>
+      </c>
       <c r="G20" t="s">
         <v>155</v>
       </c>
@@ -5426,6 +5446,9 @@
       <c r="E28">
         <v>1</v>
       </c>
+      <c r="F28" t="s">
+        <v>175</v>
+      </c>
       <c r="H28" t="s">
         <v>142</v>
       </c>
@@ -5448,6 +5471,9 @@
       <c r="E29">
         <v>-1</v>
       </c>
+      <c r="F29" t="s">
+        <v>172</v>
+      </c>
       <c r="H29" t="s">
         <v>121</v>
       </c>
@@ -5629,6 +5655,9 @@
       </c>
       <c r="E37">
         <v>5</v>
+      </c>
+      <c r="F37" t="s">
+        <v>174</v>
       </c>
       <c r="H37" t="s">
         <v>128</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87D094CE-D9FA-4F3D-8415-12253E306B6D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6D8293-DF25-4B8F-943F-19607833ACE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="D35" t="str">
         <f>VLOOKUP(InputData[[#This Row],[発動条件]],選択用フィールド!$A$2:$B$6,2,FALSE)</f>
-        <v>StartEffect</v>
+        <v>SkillEffect</v>
       </c>
       <c r="E35">
         <f>InputData[[#This Row],[クールタイム]]</f>
@@ -5601,7 +5601,7 @@
         <v>逆位置</v>
       </c>
       <c r="C35" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="D35">
         <v>-1</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE6D8293-DF25-4B8F-943F-19607833ACE1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3073211-2C12-4D65-B6FF-6AA60FBC81A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="191">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1145,10 +1145,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Counter</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>FlipCamera</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -1216,6 +1212,62 @@
   </si>
   <si>
     <t>Staraura</t>
+  </si>
+  <si>
+    <t>Buff</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Debuff</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Heal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Dice</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Purification</t>
+  </si>
+  <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Stan</t>
+  </si>
+  <si>
+    <t>TimeStop</t>
+  </si>
+  <si>
+    <t>BulletRain</t>
+  </si>
+  <si>
+    <t>ArcanaSkill</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ArcanaSkill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ster</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Blink</t>
+  </si>
+  <si>
+    <t>Installation</t>
+  </si>
+  <si>
+    <t>Up</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -2657,7 +2709,7 @@
       </c>
       <c r="H6" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Buff</v>
       </c>
       <c r="I6" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2703,7 +2755,7 @@
       </c>
       <c r="H7" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Debuff</v>
       </c>
       <c r="I7" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2749,7 +2801,7 @@
       </c>
       <c r="H8" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Heal</v>
       </c>
       <c r="I8" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2795,7 +2847,7 @@
       </c>
       <c r="H9" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Dice</v>
       </c>
       <c r="I9" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -2841,7 +2893,7 @@
       </c>
       <c r="H10" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Stan</v>
       </c>
       <c r="I10" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3439,7 +3491,7 @@
       </c>
       <c r="H23" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Stan</v>
       </c>
       <c r="I23" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3531,7 +3583,7 @@
       </c>
       <c r="H25" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/Counter</v>
+        <v>Audio/SE/ArcanaSkill</v>
       </c>
       <c r="I25" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3669,7 +3721,7 @@
       </c>
       <c r="H28" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Up</v>
       </c>
       <c r="I28" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3715,7 +3767,7 @@
       </c>
       <c r="H29" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Heal</v>
       </c>
       <c r="I29" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3899,7 +3951,7 @@
       </c>
       <c r="H33" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Purification</v>
       </c>
       <c r="I33" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -3945,7 +3997,7 @@
       </c>
       <c r="H34" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Installation</v>
       </c>
       <c r="I34" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4037,7 +4089,7 @@
       </c>
       <c r="H36" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Ster</v>
       </c>
       <c r="I36" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4083,7 +4135,7 @@
       </c>
       <c r="H37" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/ArcanaSkill</v>
       </c>
       <c r="I37" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4129,7 +4181,7 @@
       </c>
       <c r="H38" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Blink</v>
       </c>
       <c r="I38" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4175,7 +4227,7 @@
       </c>
       <c r="H39" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Summon</v>
       </c>
       <c r="I39" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4221,7 +4273,7 @@
       </c>
       <c r="H40" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Alert</v>
       </c>
       <c r="I40" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4267,7 +4319,7 @@
       </c>
       <c r="H41" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/TimeStop</v>
       </c>
       <c r="I41" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4313,7 +4365,7 @@
       </c>
       <c r="H42" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/Bullet</v>
       </c>
       <c r="I42" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4359,7 +4411,7 @@
       </c>
       <c r="H43" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
-        <v>Audio/SE/</v>
+        <v>Audio/SE/BulletRain</v>
       </c>
       <c r="I43" t="str">
         <f>InputData[[#This Row],[説明]]</f>
@@ -4903,7 +4955,10 @@
         <v>1.05</v>
       </c>
       <c r="F6" t="s">
-        <v>168</v>
+        <v>167</v>
+      </c>
+      <c r="G6" t="s">
+        <v>175</v>
       </c>
       <c r="H6" t="s">
         <v>100</v>
@@ -4928,7 +4983,10 @@
         <v>0.99</v>
       </c>
       <c r="F7" t="s">
-        <v>169</v>
+        <v>168</v>
+      </c>
+      <c r="G7" t="s">
+        <v>176</v>
       </c>
       <c r="H7" t="s">
         <v>101</v>
@@ -4953,7 +5011,10 @@
         <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>170</v>
+        <v>169</v>
+      </c>
+      <c r="G8" t="s">
+        <v>177</v>
       </c>
       <c r="H8" t="s">
         <v>102</v>
@@ -4980,6 +5041,9 @@
       <c r="F9" t="s">
         <v>135</v>
       </c>
+      <c r="G9" t="s">
+        <v>178</v>
+      </c>
       <c r="H9" t="s">
         <v>103</v>
       </c>
@@ -5002,6 +5066,9 @@
       <c r="E10">
         <v>15</v>
       </c>
+      <c r="G10" t="s">
+        <v>181</v>
+      </c>
       <c r="H10" t="s">
         <v>104</v>
       </c>
@@ -5069,7 +5136,7 @@
         <v>15</v>
       </c>
       <c r="F13" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="G13" t="s">
         <v>151</v>
@@ -5097,7 +5164,7 @@
         <v>5</v>
       </c>
       <c r="F14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="G14" t="s">
         <v>152</v>
@@ -5216,7 +5283,7 @@
         <v>0.05</v>
       </c>
       <c r="F19" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G19" t="s">
         <v>154</v>
@@ -5244,7 +5311,7 @@
         <v>-1</v>
       </c>
       <c r="F20" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G20" t="s">
         <v>155</v>
@@ -5324,6 +5391,9 @@
       <c r="E23">
         <v>10</v>
       </c>
+      <c r="G23" t="s">
+        <v>181</v>
+      </c>
       <c r="H23" t="s">
         <v>117</v>
       </c>
@@ -5372,10 +5442,10 @@
         <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G25" t="s">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="H25" t="s">
         <v>118</v>
@@ -5400,7 +5470,7 @@
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H26" t="s">
         <v>119</v>
@@ -5447,7 +5517,10 @@
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>175</v>
+        <v>174</v>
+      </c>
+      <c r="G28" t="s">
+        <v>190</v>
       </c>
       <c r="H28" t="s">
         <v>142</v>
@@ -5472,7 +5545,10 @@
         <v>-1</v>
       </c>
       <c r="F29" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+      <c r="G29" t="s">
+        <v>177</v>
       </c>
       <c r="H29" t="s">
         <v>121</v>
@@ -5541,7 +5617,7 @@
         <v>-1</v>
       </c>
       <c r="H32" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.45">
@@ -5562,6 +5638,9 @@
       <c r="E33">
         <v>0.05</v>
       </c>
+      <c r="G33" t="s">
+        <v>179</v>
+      </c>
       <c r="H33" t="s">
         <v>124</v>
       </c>
@@ -5587,6 +5666,9 @@
       <c r="F34" t="s">
         <v>137</v>
       </c>
+      <c r="G34" t="s">
+        <v>189</v>
+      </c>
       <c r="H34" t="s">
         <v>125</v>
       </c>
@@ -5610,7 +5692,7 @@
         <v>0.5</v>
       </c>
       <c r="G35" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H35" t="s">
         <v>126</v>
@@ -5634,6 +5716,9 @@
       <c r="E36">
         <v>15</v>
       </c>
+      <c r="G36" t="s">
+        <v>187</v>
+      </c>
       <c r="H36" t="s">
         <v>127</v>
       </c>
@@ -5657,7 +5742,10 @@
         <v>5</v>
       </c>
       <c r="F37" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="G37" t="s">
+        <v>186</v>
       </c>
       <c r="H37" t="s">
         <v>128</v>
@@ -5681,8 +5769,11 @@
       <c r="E38">
         <v>5</v>
       </c>
+      <c r="G38" t="s">
+        <v>188</v>
+      </c>
       <c r="H38" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.45">
@@ -5706,6 +5797,9 @@
       <c r="F39" t="s">
         <v>146</v>
       </c>
+      <c r="G39" t="s">
+        <v>150</v>
+      </c>
       <c r="H39" t="s">
         <v>145</v>
       </c>
@@ -5729,7 +5823,10 @@
         <v>15</v>
       </c>
       <c r="F40" t="s">
-        <v>171</v>
+        <v>170</v>
+      </c>
+      <c r="G40" t="s">
+        <v>180</v>
       </c>
       <c r="H40" t="s">
         <v>129</v>
@@ -5753,6 +5850,9 @@
       <c r="E41">
         <v>3</v>
       </c>
+      <c r="G41" t="s">
+        <v>182</v>
+      </c>
       <c r="H41" t="s">
         <v>130</v>
       </c>
@@ -5778,6 +5878,9 @@
       <c r="F42" t="s">
         <v>143</v>
       </c>
+      <c r="G42" t="s">
+        <v>185</v>
+      </c>
       <c r="H42" t="s">
         <v>144</v>
       </c>
@@ -5803,6 +5906,9 @@
       <c r="F43" t="s">
         <v>138</v>
       </c>
+      <c r="G43" t="s">
+        <v>183</v>
+      </c>
       <c r="H43" t="s">
         <v>131</v>
       </c>
@@ -5848,7 +5954,7 @@
         <v>-1</v>
       </c>
       <c r="G45" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H45" t="s">
         <v>133</v>

--- a/Assets/StreamingAssets/Excel/ArcanaData.xlsx
+++ b/Assets/StreamingAssets/Excel/ArcanaData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Create\Git\Arcanumber\Assets\StreamingAssets\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3073211-2C12-4D65-B6FF-6AA60FBC81A8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70E305DA-821D-4D06-B5F6-E02D045162AA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{AC75F782-5E9E-4D3C-BA30-1B913C01DC7F}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="191">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -1230,43 +1230,44 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>Alert</t>
+  </si>
+  <si>
+    <t>Stan</t>
+  </si>
+  <si>
+    <t>TimeStop</t>
+  </si>
+  <si>
+    <t>BulletRain</t>
+  </si>
+  <si>
+    <t>ArcanaSkill</t>
+  </si>
+  <si>
+    <t>Bullet</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ArcanaSkill</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Ster</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Blink</t>
+  </si>
+  <si>
+    <t>Installation</t>
+  </si>
+  <si>
+    <t>Up</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>Purification</t>
-  </si>
-  <si>
-    <t>Alert</t>
-  </si>
-  <si>
-    <t>Stan</t>
-  </si>
-  <si>
-    <t>TimeStop</t>
-  </si>
-  <si>
-    <t>BulletRain</t>
-  </si>
-  <si>
-    <t>ArcanaSkill</t>
-  </si>
-  <si>
-    <t>Bullet</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ArcanaSkill</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Ster</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Blink</t>
-  </si>
-  <si>
-    <t>Installation</t>
-  </si>
-  <si>
-    <t>Up</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3947,7 +3948,7 @@
       </c>
       <c r="G33" t="str">
         <f>選択用フィールド!$G$2&amp;"/"&amp;InputData[[#This Row],[エフェクト]]</f>
-        <v>Effect/Arcana/</v>
+        <v>Effect/Arcana/Buff</v>
       </c>
       <c r="H33" t="str">
         <f>選択用フィールド!$G$5&amp;"/"&amp;InputData[[#This Row],[効果音]]</f>
@@ -5067,7 +5068,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
         <v>104</v>
@@ -5392,7 +5393,7 @@
         <v>10</v>
       </c>
       <c r="G23" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H23" t="s">
         <v>117</v>
@@ -5445,7 +5446,7 @@
         <v>165</v>
       </c>
       <c r="G25" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H25" t="s">
         <v>118</v>
@@ -5520,7 +5521,7 @@
         <v>174</v>
       </c>
       <c r="G28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H28" t="s">
         <v>142</v>
@@ -5638,8 +5639,11 @@
       <c r="E33">
         <v>0.05</v>
       </c>
+      <c r="F33" t="s">
+        <v>167</v>
+      </c>
       <c r="G33" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="H33" t="s">
         <v>124</v>
@@ -5667,7 +5671,7 @@
         <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H34" t="s">
         <v>125</v>
@@ -5717,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H36" t="s">
         <v>127</v>
@@ -5745,7 +5749,7 @@
         <v>173</v>
       </c>
       <c r="G37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H37" t="s">
         <v>128</v>
@@ -5770,7 +5774,7 @@
         <v>5</v>
       </c>
       <c r="G38" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H38" t="s">
         <v>162</v>
@@ -5826,7 +5830,7 @@
         <v>170</v>
       </c>
       <c r="G40" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H40" t="s">
         <v>129</v>
@@ -5851,7 +5855,7 @@
         <v>3</v>
       </c>
       <c r="G41" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H41" t="s">
         <v>130</v>
@@ -5879,7 +5883,7 @@
         <v>143</v>
       </c>
       <c r="G42" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H42" t="s">
         <v>144</v>
@@ -5907,7 +5911,7 @@
         <v>138</v>
       </c>
       <c r="G43" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H43" t="s">
         <v>131</v>
